--- a/jogos_2025-03-11.xlsx
+++ b/jogos_2025-03-11.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -825,22 +825,22 @@
         <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AA3" t="n">
         <v>3.08</v>
@@ -849,32 +849,32 @@
         <v>1.28</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['4', '29']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['58', '67', '80', '90+6']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45727.4375</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.73</v>
+        <v>6.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
         <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '71']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['4', '29']</t>
+          <t>['2', '9']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45727.4375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.83</v>
+        <v>4.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08</v>
+        <v>3.63</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['45', '61']</t>
+          <t>['13', '45', '56', '65', '88']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['17', '90+5']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45727.4375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1177,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>2.83</v>
       </c>
       <c r="M6" t="n">
-        <v>6.2</v>
+        <v>3.08</v>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.66</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD6" t="n">
         <v>2</v>
       </c>
-      <c r="AA6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['5', '71']</t>
+          <t>['45', '61']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['2', '9']</t>
+          <t>['17', '90+5']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45727.4375</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>3.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['13', '45', '56', '65', '88']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['58', '67', '80', '90+6']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45727.4375</v>
@@ -1536,35 +1536,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['56', '64', '88']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['41', '84']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.42</v>
       </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI9" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45727.54166666666</v>
@@ -1665,119 +1665,119 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['56', '64', '88']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['41', '84']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45727.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,80 +2088,80 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.69</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA13" t="n">
         <v>4.75</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['47', '73']</t>
+          <t>['13', '19', '90+3']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
         <v>2.6</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.95</v>
+        <v>1.86</v>
       </c>
       <c r="M15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.55</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2409,20 +2409,20 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,87 +2449,87 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.56</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.46</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>4.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['13', '19', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['31', '71', '77']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2707,91 +2707,91 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['51', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.62</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
         <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
         <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>['51', '87']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['31', '71', '77']</t>
-        </is>
-      </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.66</v>
+        <v>4.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45727.60416666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Legnago Salus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="O20" t="n">
-        <v>3.61</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.56</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
         <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X20" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.98</v>
+        <v>4.45</v>
       </c>
       <c r="AB20" t="n">
         <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '77', '90+1']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45727.60416666666</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Legnago Salus</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.16</v>
+        <v>1.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['28', '77', '90+1']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45727.60416666666</v>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>4.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X22" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['47', '73']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.78</v>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45727.60416666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,65 +3378,65 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="S23" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="X23" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45727.60416666666</v>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hannover 96 II</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>4.87</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>5.87</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['8', '26', '84']</t>
+          <t>['20', '34']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['31', '53']</t>
         </is>
       </c>
       <c r="AG25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.42</v>
       </c>
-      <c r="AH25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45727.625</v>
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.91</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="N26" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.25</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['8', '26', '84']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['53', '84']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45727.625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unterhaching</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4015,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.67</v>
+        <v>2.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
         <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
         <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['3', '10']</t>
+          <t>['53', '84']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45727.625</v>
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Unterhaching</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hannover 96 II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
       <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.46</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.7</v>
       </c>
-      <c r="T29" t="n">
+      <c r="Y29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.05</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['3', '10']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.68</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['20', '34']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['31', '53']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.95</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45727.625</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="P30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['17', '73', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['11', '39']</t>
+          <t>['24', '30', '35']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45727.66666666666</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>3.73</v>
+        <v>4.05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>4.02</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
         <v>1.29</v>
@@ -4434,31 +4434,31 @@
         <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.53</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z31" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" t="n">
         <v>2.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC31" t="n">
         <v>1.5</v>
@@ -4468,25 +4468,25 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>['56', '59', '76']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['38', '66']</t>
-        </is>
-      </c>
       <c r="AG31" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45727.66666666666</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4.05</v>
+        <v>3.73</v>
       </c>
       <c r="N32" t="n">
-        <v>4.02</v>
+        <v>2.04</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R32" t="n">
         <v>1.29</v>
@@ -4563,31 +4563,31 @@
         <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.57</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
         <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
         <v>1.5</v>
@@ -4597,25 +4597,25 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['56', '59', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '66']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45727.66666666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="M33" t="n">
-        <v>4.65</v>
+        <v>3.71</v>
       </c>
       <c r="N33" t="n">
-        <v>5.29</v>
+        <v>3.73</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.22</v>
       </c>
-      <c r="S33" t="n">
+      <c r="X33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" t="n">
+      <c r="Y33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.1</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '73', '87']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['24', '30', '35']</t>
+          <t>['11', '39']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45727.66666666666</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="M34" t="n">
-        <v>2.69</v>
+        <v>3.41</v>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>1.77</v>
       </c>
       <c r="O34" t="n">
-        <v>4.31</v>
+        <v>4.64</v>
       </c>
       <c r="P34" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.21</v>
+        <v>2.41</v>
       </c>
       <c r="R34" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>2.81</v>
       </c>
       <c r="U34" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="X34" t="n">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['27', '30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45727.6875</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,25 +4926,25 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.62</v>
+        <v>3.07</v>
       </c>
       <c r="M35" t="n">
         <v>2.69</v>
       </c>
       <c r="N35" t="n">
-        <v>3.21</v>
+        <v>2.68</v>
       </c>
       <c r="O35" t="n">
-        <v>3.51</v>
+        <v>3.87</v>
       </c>
       <c r="P35" t="n">
         <v>1.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="R35" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S35" t="n">
         <v>2.17</v>
@@ -4956,7 +4956,7 @@
         <v>1.19</v>
       </c>
       <c r="V35" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W35" t="n">
         <v>1.63</v>
@@ -4965,26 +4965,26 @@
         <v>2.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['61', '68']</t>
+          <t>['66', '80']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45727.6875</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.41</v>
+        <v>2.69</v>
       </c>
       <c r="N36" t="n">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>4.64</v>
+        <v>4.31</v>
       </c>
       <c r="P36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S36" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q36" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.05</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>3.65</v>
       </c>
       <c r="U36" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>3.34</v>
+        <v>2.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '30']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45727.6875</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,25 +5184,25 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.07</v>
+        <v>2.62</v>
       </c>
       <c r="M37" t="n">
         <v>2.69</v>
       </c>
       <c r="N37" t="n">
-        <v>2.68</v>
+        <v>3.21</v>
       </c>
       <c r="O37" t="n">
-        <v>3.87</v>
+        <v>3.51</v>
       </c>
       <c r="P37" t="n">
         <v>1.83</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S37" t="n">
         <v>2.17</v>
@@ -5214,7 +5214,7 @@
         <v>1.19</v>
       </c>
       <c r="V37" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W37" t="n">
         <v>1.63</v>
@@ -5223,26 +5223,26 @@
         <v>2.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['66', '80']</t>
+          <t>['61', '68']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45727.6875</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,19 +5287,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>1.67</v>
+        <v>6.2</v>
       </c>
       <c r="O38" t="n">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="P38" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.35</v>
+        <v>6.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X38" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['18', '79']</t>
+          <t>['27', '47']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['56', '90+3']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.16</v>
+        <v>2.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.1</v>
+        <v>1.38</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45727.69791666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M39" t="n">
-        <v>4.33</v>
+        <v>3.47</v>
       </c>
       <c r="N39" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P39" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="T39" t="n">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="X39" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['22', '38', '54', '81']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45727.69791666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="M40" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="N40" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
         <v>2.75</v>
       </c>
-      <c r="P40" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T40" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.25</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="AC40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['57', '80']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.55</v>
       </c>
-      <c r="X40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45727.69791666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
         <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="M41" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N41" t="n">
         <v>5</v>
       </c>
-      <c r="N41" t="n">
-        <v>15</v>
-      </c>
       <c r="O41" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U41" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['11', '58']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AJ41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45727.69791666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>3.4</v>
       </c>
       <c r="M42" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>7.2</v>
+        <v>2.04</v>
       </c>
       <c r="O42" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI42" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X42" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['7', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AJ42" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45727.69791666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,65 +5958,65 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.33</v>
+        <v>3.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N43" t="n">
-        <v>3.12</v>
+        <v>1.98</v>
       </c>
       <c r="O43" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="X43" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AC43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD43" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['76', '90+1']</t>
+          <t>['23', '48']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI43" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.82</v>
+        <v>3.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>1.74</v>
       </c>
       <c r="O44" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
         <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="R44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.57</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['30', '72']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.82</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AI44" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Newtown</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.68</v>
+        <v>1.66</v>
       </c>
       <c r="M45" t="n">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="N45" t="n">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X45" t="n">
         <v>3.1</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Y45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH45" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q45" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="AI45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>3.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.88</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,23 +6319,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['8', '49']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
         <v>1.66</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="N46" t="n">
-        <v>5</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="AH46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI46" t="n">
         <v>2.3</v>
       </c>
-      <c r="P46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ46" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="M47" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>1.46</v>
+        <v>2.6</v>
       </c>
       <c r="P47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA47" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['45+1', '90+4']</t>
+          <t>['16', '35']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '72', '76']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AJ47" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,34 +6603,34 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
         <v>1.05</v>
@@ -6639,13 +6639,13 @@
         <v>1.28</v>
       </c>
       <c r="X48" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AA48" t="n">
         <v>3.1</v>
@@ -6654,32 +6654,32 @@
         <v>1.36</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['16', '35']</t>
+          <t>['17', '54']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['64', '72', '76']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newtown</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,65 +6732,65 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.09</v>
+        <v>2.68</v>
       </c>
       <c r="M49" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="N49" t="n">
-        <v>3.57</v>
+        <v>2.37</v>
       </c>
       <c r="O49" t="n">
         <v>3.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>2.87</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T49" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="X49" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AA49" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['34', '86']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O50" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q50" t="n">
         <v>2.35</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC50" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD50" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '79']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['5', '90+2']</t>
+          <t>['56', '90+3']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45727.69791666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3.59</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="O51" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD51" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['24', '79']</t>
+          <t>['5', '90+2']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,16 +7093,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="M52" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="N52" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
         <v>2.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U52" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="X52" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['6', '63', '88']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['30', '72']</t>
+          <t>['38', '70']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="N54" t="n">
-        <v>2.04</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.88</v>
+        <v>9.25</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S54" t="n">
-        <v>2.63</v>
+        <v>4.4</v>
       </c>
       <c r="T54" t="n">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="U54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X54" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y54" t="n">
         <v>1.33</v>
       </c>
-      <c r="V54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y54" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA54" t="n">
-        <v>3.85</v>
+        <v>1.85</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC54" t="n">
         <v>1.95</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
+          <t>['45+1', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
       <c r="AG54" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.33</v>
+        <v>5.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.67</v>
+        <v>4.75</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,109 +7609,109 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['76', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI56" t="n">
         <v>2</v>
       </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O56" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P56" t="n">
+      <c r="AJ56" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['6', '63', '88']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['38', '70']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.57</v>
+        <v>2.17</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>2.99</v>
       </c>
       <c r="N57" t="n">
-        <v>2.47</v>
+        <v>3.65</v>
       </c>
       <c r="O57" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="P57" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U57" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V57" t="n">
         <v>1.05</v>
       </c>
       <c r="W57" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="X57" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['8', '49']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,19 +7867,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M58" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="O58" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="P58" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q58" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="R58" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S58" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T58" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U58" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V58" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X58" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['27', '47']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45727.69791666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8014,7 +8014,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="M59" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA59" t="n">
         <v>4</v>
       </c>
-      <c r="N59" t="n">
-        <v>6</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R59" t="n">
+      <c r="AB59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['34', '86']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
         <v>1.36</v>
       </c>
-      <c r="S59" t="n">
-        <v>3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X59" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>['17', '54']</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH59" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ59" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45727.69791666666</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8140,10 +8140,10 @@
         <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.61</v>
+        <v>1.72</v>
       </c>
       <c r="M60" t="n">
-        <v>3.28</v>
+        <v>3.59</v>
       </c>
       <c r="N60" t="n">
-        <v>2.61</v>
+        <v>4.75</v>
       </c>
       <c r="O60" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P60" t="n">
         <v>2.1</v>
       </c>
       <c r="Q60" t="n">
+        <v>5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T60" t="n">
         <v>3.25</v>
       </c>
-      <c r="R60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
       <c r="U60" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V60" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W60" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X60" t="n">
-        <v>3.09</v>
+        <v>3.45</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.83</v>
+        <v>3.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD60" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['57', '80']</t>
+          <t>['24', '79']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45727.69791666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
         <v>2</v>
       </c>
-      <c r="H61" t="n">
-        <v>1</v>
-      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -8280,28 +8280,28 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.66</v>
+        <v>2.72</v>
       </c>
       <c r="M61" t="n">
-        <v>3.73</v>
+        <v>3.19</v>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>2.57</v>
       </c>
       <c r="O61" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
         <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R61" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T61" t="n">
         <v>2.63</v>
@@ -8310,53 +8310,53 @@
         <v>1.44</v>
       </c>
       <c r="V61" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W61" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X61" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="Y61" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z61" t="n">
         <v>1.79</v>
       </c>
-      <c r="Z61" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA61" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['11', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['56', '88']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="AH61" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45727.69791666666</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,22 +8383,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -8409,22 +8409,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.72</v>
+        <v>1.34</v>
       </c>
       <c r="M62" t="n">
-        <v>3.19</v>
+        <v>5.5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.57</v>
+        <v>7.2</v>
       </c>
       <c r="O62" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="R62" t="n">
         <v>1.33</v>
@@ -8433,59 +8433,59 @@
         <v>3.25</v>
       </c>
       <c r="T62" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U62" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V62" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W62" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X62" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AB62" t="n">
         <v>1.44</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '90+2']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['56', '88']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45727.69791666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,23 +8512,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>2</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
@@ -8538,65 +8538,65 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="M63" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>5.1</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P63" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T63" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U63" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V63" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W63" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X63" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['23', '48']</t>
+          <t>['22', '38', '54', '81']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -8605,16 +8605,16 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45727.69791666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,16 +8770,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="M65" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA65" t="n">
         <v>4</v>
       </c>
-      <c r="N65" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U65" t="n">
+      <c r="AB65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI65" t="n">
         <v>1.57</v>
       </c>
-      <c r="V65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X65" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ65" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45727.70833333334</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,19 +9028,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.89</v>
+        <v>3.74</v>
       </c>
       <c r="M67" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="N67" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="O67" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="R67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U67" t="n">
         <v>1.44</v>
       </c>
-      <c r="S67" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W67" t="n">
         <v>1.33</v>
       </c>
-      <c r="V67" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X67" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['51', '55']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ67" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45727.70833333334</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,25 +9157,25 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.74</v>
+        <v>1.92</v>
       </c>
       <c r="M68" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>1.85</v>
+        <v>3.76</v>
       </c>
       <c r="O68" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T68" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="U68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X68" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD68" t="n">
         <v>2.5</v>
       </c>
-      <c r="R68" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X68" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC68" t="n">
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI68" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD68" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>['51', '55']</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG68" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ68" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45727.70833333334</v>
